--- a/WIP/月茗/新建 XLSX 工作表.xlsx
+++ b/WIP/月茗/新建 XLSX 工作表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="420" activeTab="1"/>
+    <workbookView windowWidth="29115" windowHeight="17655" tabRatio="420"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="120">
+  <si>
+    <t>魔王军</t>
+  </si>
   <si>
     <t>序号</t>
   </si>
@@ -37,58 +40,43 @@
     <t>国策</t>
   </si>
   <si>
+    <t>团结一致</t>
+  </si>
+  <si>
+    <t>加强中央管理</t>
+  </si>
+  <si>
+    <t>承诺自治权利</t>
+  </si>
+  <si>
+    <t>联席会议</t>
+  </si>
+  <si>
+    <t>向地方投资</t>
+  </si>
+  <si>
+    <t>中央政治局</t>
+  </si>
+  <si>
+    <t>组建顾问团队</t>
+  </si>
+  <si>
+    <t>在魔王城说早安</t>
+  </si>
+  <si>
     <t>介绍</t>
   </si>
   <si>
+    <t>清洗行动带来的余波比我们想象到还要久一些，我们必须立即行动，消除负面影响。</t>
+  </si>
+  <si>
+    <t>“风暴之眼”行动已经证明了魔族并不是只有武力没有脑子的傻大个，我们同样能够精诚合作。成立一个常驻的联席会议机制能够有效的保持这种能力。</t>
+  </si>
+  <si>
+    <t>尽管有着情报单位统筹，地方在配合上仍然心有余而力不足，甚至几次差点导致行动失败。通过向地方倾斜更多的资源，我们应当能够推进这一问题的解决进度。</t>
+  </si>
+  <si>
     <t>效果</t>
-  </si>
-  <si>
-    <t>可点击条件</t>
-  </si>
-  <si>
-    <t>跳过条件</t>
-  </si>
-  <si>
-    <t>其他</t>
-  </si>
-  <si>
-    <t>团结一致</t>
-  </si>
-  <si>
-    <t>加强中央管理</t>
-  </si>
-  <si>
-    <t>承诺自治权利</t>
-  </si>
-  <si>
-    <t>联席会议</t>
-  </si>
-  <si>
-    <t>向地方投资</t>
-  </si>
-  <si>
-    <t>所有其他在阵营中的国家获得2个民工2个军工</t>
-  </si>
-  <si>
-    <t>魔王军</t>
-  </si>
-  <si>
-    <t>中央政治局</t>
-  </si>
-  <si>
-    <t>组建顾问团队</t>
-  </si>
-  <si>
-    <t>在魔王城说早安</t>
-  </si>
-  <si>
-    <t>清洗行动带来的余波比我们想象到还要久一些，我们必须立即行动，消除负面影响。</t>
-  </si>
-  <si>
-    <t>“风暴之眼”行动已经证明了魔族并不是只有武力没有脑子的傻大个，我们同样能够精诚合作。成立一个常驻的联席会议机制能够有效的保持这种能力。</t>
-  </si>
-  <si>
-    <t>尽管有着情报单位统筹，地方在配合上仍然心有余而力不足，甚至几次差点导致行动失败。通过向地方倾斜更多的资源，我们应当能够推进这一问题的解决进度。</t>
   </si>
   <si>
     <t>“风暴余波”追加效果：稳定+10，战争+10
@@ -110,6 +98,9 @@
 魔族臣服度向右移动</t>
   </si>
   <si>
+    <t>所有其他在阵营中的国家获得2个民工2个军工</t>
+  </si>
+  <si>
     <t>提升政府效率
 获得”中央政治局“：pp+5%</t>
   </si>
@@ -125,10 +116,19 @@
 解锁首都建设决议</t>
   </si>
   <si>
+    <t>可点击条件</t>
+  </si>
+  <si>
     <t>拥有国家精神“风暴余波”</t>
   </si>
   <si>
     <t>没有国家精神“风暴余波”</t>
+  </si>
+  <si>
+    <t>跳过条件</t>
+  </si>
+  <si>
+    <t>其他</t>
   </si>
   <si>
     <t>东征</t>
@@ -1441,7 +1441,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.625" style="7"/>
@@ -1449,155 +1449,13 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:7">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:7">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:7">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:7">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:7">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:7">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:7">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:7">
-      <c r="A9" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:7">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:7">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:7">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:7">
-      <c r="A13" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:7">
-      <c r="A14" s="7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:7">
-      <c r="A15" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:7">
-      <c r="A16" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:1">
-      <c r="A17" s="7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:1">
-      <c r="A18" s="7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:1">
-      <c r="A19" s="7">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:1">
-      <c r="A20" s="7">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:1">
-      <c r="A21" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:1">
-      <c r="A22" s="7">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:1">
-      <c r="A23" s="7">
-        <v>22</v>
-      </c>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1617,7 +1475,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:9">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1630,7 +1488,7 @@
     </row>
     <row r="2" customHeight="1" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -1659,47 +1517,47 @@
     </row>
     <row r="3" customHeight="1" spans="1:9">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:9">
       <c r="A4" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -1707,45 +1565,45 @@
     </row>
     <row r="5" customHeight="1" spans="1:9">
       <c r="A5" s="3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:9">
       <c r="A6" s="3" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -1755,7 +1613,7 @@
     </row>
     <row r="7" customHeight="1" spans="1:9">
       <c r="A7" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1768,7 +1626,7 @@
     </row>
     <row r="8" customHeight="1" spans="1:9">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1781,7 +1639,7 @@
     </row>
     <row r="9" customHeight="1" spans="1:9">
       <c r="A9" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" s="5">
         <v>9</v>
@@ -1810,7 +1668,7 @@
     </row>
     <row r="10" customHeight="1" spans="1:9">
       <c r="A10" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>29</v>
@@ -1837,7 +1695,7 @@
     </row>
     <row r="11" customHeight="1" spans="1:9">
       <c r="A11" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1850,7 +1708,7 @@
     </row>
     <row r="12" customHeight="1" spans="1:9">
       <c r="A12" s="5" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>36</v>
@@ -1867,7 +1725,7 @@
     </row>
     <row r="13" customHeight="1" spans="1:9">
       <c r="A13" s="5" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>38</v>
@@ -1884,7 +1742,7 @@
     </row>
     <row r="14" customHeight="1" spans="1:9">
       <c r="A14" s="5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1897,7 +1755,7 @@
     </row>
     <row r="15" customHeight="1" spans="1:9">
       <c r="A15" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1910,7 +1768,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:9">
       <c r="A16" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16" s="3">
         <v>17</v>
@@ -1939,7 +1797,7 @@
     </row>
     <row r="17" customHeight="1" spans="1:9">
       <c r="A17" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>40</v>
@@ -1966,7 +1824,7 @@
     </row>
     <row r="18" customHeight="1" spans="1:9">
       <c r="A18" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1979,7 +1837,7 @@
     </row>
     <row r="19" customHeight="1" spans="1:9">
       <c r="A19" s="3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1992,7 +1850,7 @@
     </row>
     <row r="20" customHeight="1" spans="1:9">
       <c r="A20" s="3" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -2005,7 +1863,7 @@
     </row>
     <row r="21" customHeight="1" spans="1:9">
       <c r="A21" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -2018,7 +1876,7 @@
     </row>
     <row r="22" customHeight="1" spans="1:9">
       <c r="A22" s="3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -2031,7 +1889,7 @@
     </row>
     <row r="23" customHeight="1" spans="1:9">
       <c r="A23" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B23" s="5">
         <v>25</v>
@@ -2060,7 +1918,7 @@
     </row>
     <row r="24" customHeight="1" spans="1:9">
       <c r="A24" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>47</v>
@@ -2089,7 +1947,7 @@
     </row>
     <row r="25" customHeight="1" spans="1:9">
       <c r="A25" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -2102,7 +1960,7 @@
     </row>
     <row r="26" customHeight="1" spans="1:9">
       <c r="A26" s="5" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>55</v>
@@ -2129,7 +1987,7 @@
     </row>
     <row r="27" customHeight="1" spans="1:9">
       <c r="A27" s="5" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -2142,7 +2000,7 @@
     </row>
     <row r="28" customHeight="1" spans="1:9">
       <c r="A28" s="5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -2155,7 +2013,7 @@
     </row>
     <row r="29" customHeight="1" spans="1:9">
       <c r="A29" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2168,7 +2026,7 @@
     </row>
     <row r="30" customHeight="1" spans="1:9">
       <c r="A30" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" s="3">
         <v>33</v>
@@ -2197,7 +2055,7 @@
     </row>
     <row r="31" customHeight="1" spans="1:9">
       <c r="A31" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>62</v>
@@ -2226,7 +2084,7 @@
     </row>
     <row r="32" customHeight="1" spans="1:9">
       <c r="A32" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -2239,7 +2097,7 @@
     </row>
     <row r="33" customHeight="1" spans="1:9">
       <c r="A33" s="3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>70</v>
@@ -2262,7 +2120,7 @@
     </row>
     <row r="34" customHeight="1" spans="1:9">
       <c r="A34" s="3" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>75</v>
@@ -2277,7 +2135,7 @@
     </row>
     <row r="35" customHeight="1" spans="1:9">
       <c r="A35" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -2290,7 +2148,7 @@
     </row>
     <row r="36" customHeight="1" spans="1:9">
       <c r="A36" s="3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -2303,7 +2161,7 @@
     </row>
     <row r="37" customHeight="1" spans="1:9">
       <c r="A37" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" s="5">
         <v>41</v>
@@ -2332,7 +2190,7 @@
     </row>
     <row r="38" customHeight="1" spans="1:9">
       <c r="A38" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>76</v>
@@ -2353,7 +2211,7 @@
     </row>
     <row r="39" customHeight="1" spans="1:9">
       <c r="A39" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -2366,7 +2224,7 @@
     </row>
     <row r="40" customHeight="1" spans="1:9">
       <c r="A40" s="5" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -2383,7 +2241,7 @@
     </row>
     <row r="41" customHeight="1" spans="1:9">
       <c r="A41" s="5" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -2396,7 +2254,7 @@
     </row>
     <row r="42" customHeight="1" spans="1:9">
       <c r="A42" s="5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -2409,7 +2267,7 @@
     </row>
     <row r="43" customHeight="1" spans="1:9">
       <c r="A43" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -2422,7 +2280,7 @@
     </row>
     <row r="44" customHeight="1" spans="1:9">
       <c r="A44" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B44" s="3">
         <v>49</v>
@@ -2451,7 +2309,7 @@
     </row>
     <row r="45" customHeight="1" spans="1:9">
       <c r="A45" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>82</v>
@@ -2480,7 +2338,7 @@
     </row>
     <row r="46" customHeight="1" spans="1:9">
       <c r="A46" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -2493,7 +2351,7 @@
     </row>
     <row r="47" customHeight="1" spans="1:9">
       <c r="A47" s="3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>90</v>
@@ -2508,7 +2366,7 @@
     </row>
     <row r="48" customHeight="1" spans="1:9">
       <c r="A48" s="3" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -2521,7 +2379,7 @@
     </row>
     <row r="49" customHeight="1" spans="1:9">
       <c r="A49" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -2534,7 +2392,7 @@
     </row>
     <row r="50" customHeight="1" spans="1:9">
       <c r="A50" s="3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -2547,7 +2405,7 @@
     </row>
     <row r="51" customHeight="1" spans="1:9">
       <c r="A51" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B51" s="5">
         <v>57</v>
@@ -2576,7 +2434,7 @@
     </row>
     <row r="52" customHeight="1" spans="1:9">
       <c r="A52" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>91</v>
@@ -2605,7 +2463,7 @@
     </row>
     <row r="53" customHeight="1" spans="1:9">
       <c r="A53" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -2618,7 +2476,7 @@
     </row>
     <row r="54" customHeight="1" spans="1:9">
       <c r="A54" s="5" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -2641,7 +2499,7 @@
     </row>
     <row r="55" customHeight="1" spans="1:9">
       <c r="A55" s="5" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2654,7 +2512,7 @@
     </row>
     <row r="56" customHeight="1" spans="1:9">
       <c r="A56" s="5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2667,7 +2525,7 @@
     </row>
     <row r="57" customHeight="1" spans="1:9">
       <c r="A57" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -2680,7 +2538,7 @@
     </row>
     <row r="58" customHeight="1" spans="1:9">
       <c r="A58" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B58" s="3">
         <v>65</v>
@@ -2709,7 +2567,7 @@
     </row>
     <row r="59" customHeight="1" spans="1:9">
       <c r="A59" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>104</v>
@@ -2738,7 +2596,7 @@
     </row>
     <row r="60" customHeight="1" spans="1:9">
       <c r="A60" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -2751,7 +2609,7 @@
     </row>
     <row r="61" customHeight="1" spans="1:9">
       <c r="A61" s="3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>112</v>
@@ -2766,7 +2624,7 @@
     </row>
     <row r="62" customHeight="1" spans="1:9">
       <c r="A62" s="3" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2779,7 +2637,7 @@
     </row>
     <row r="63" customHeight="1" spans="1:9">
       <c r="A63" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -2792,7 +2650,7 @@
     </row>
     <row r="64" customHeight="1" spans="1:9">
       <c r="A64" s="3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -2805,7 +2663,7 @@
     </row>
     <row r="65" customHeight="1" spans="1:9">
       <c r="A65" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B65" s="5">
         <v>73</v>
@@ -2834,7 +2692,7 @@
     </row>
     <row r="66" customHeight="1" spans="1:9">
       <c r="A66" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>113</v>
@@ -2863,7 +2721,7 @@
     </row>
     <row r="67" customHeight="1" spans="1:9">
       <c r="A67" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2876,7 +2734,7 @@
     </row>
     <row r="68" customHeight="1" spans="1:9">
       <c r="A68" s="5" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2889,7 +2747,7 @@
     </row>
     <row r="69" customHeight="1" spans="1:9">
       <c r="A69" s="5" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2902,7 +2760,7 @@
     </row>
     <row r="70" customHeight="1" spans="1:9">
       <c r="A70" s="5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -2915,7 +2773,7 @@
     </row>
     <row r="71" customHeight="1" spans="1:9">
       <c r="A71" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2928,7 +2786,7 @@
     </row>
     <row r="72" customHeight="1" spans="1:9">
       <c r="A72" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B72" s="3">
         <v>81</v>
@@ -2957,7 +2815,7 @@
     </row>
     <row r="73" customHeight="1" spans="1:9">
       <c r="A73" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>82</v>
@@ -2986,7 +2844,7 @@
     </row>
     <row r="74" customHeight="1" spans="1:9">
       <c r="A74" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2999,7 +2857,7 @@
     </row>
     <row r="75" customHeight="1" spans="1:9">
       <c r="A75" s="3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -3012,7 +2870,7 @@
     </row>
     <row r="76" customHeight="1" spans="1:9">
       <c r="A76" s="3" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -3025,7 +2883,7 @@
     </row>
     <row r="77" customHeight="1" spans="1:9">
       <c r="A77" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -3038,7 +2896,7 @@
     </row>
     <row r="78" customHeight="1" spans="1:9">
       <c r="A78" s="3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -3051,7 +2909,7 @@
     </row>
     <row r="79" customHeight="1" spans="1:9">
       <c r="A79" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B79" s="5">
         <v>89</v>
@@ -3080,7 +2938,7 @@
     </row>
     <row r="80" customHeight="1" spans="1:9">
       <c r="A80" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>91</v>
@@ -3109,7 +2967,7 @@
     </row>
     <row r="81" customHeight="1" spans="1:9">
       <c r="A81" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -3122,7 +2980,7 @@
     </row>
     <row r="82" customHeight="1" spans="1:9">
       <c r="A82" s="5" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -3135,7 +2993,7 @@
     </row>
     <row r="83" customHeight="1" spans="1:9">
       <c r="A83" s="5" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -3148,7 +3006,7 @@
     </row>
     <row r="84" customHeight="1" spans="1:9">
       <c r="A84" s="5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -3161,7 +3019,7 @@
     </row>
     <row r="85" customHeight="1" spans="1:9">
       <c r="A85" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
